--- a/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
+++ b/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1943</v>
+        <v>0.196251</v>
       </c>
       <c r="E2" t="n">
-        <v>0.189381</v>
+        <v>0.193333</v>
       </c>
       <c r="F2" t="n">
         <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1057</v>
+        <v>-0.103749</v>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.131354</v>
+        <v>0.133765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.13812</v>
+        <v>0.139377</v>
       </c>
       <c r="F3" t="n">
         <v>0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.218646</v>
+        <v>-0.216235</v>
       </c>
       <c r="H3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.403745</v>
+        <v>0.403043</v>
       </c>
       <c r="E4" t="n">
-        <v>0.267504</v>
+        <v>0.265596</v>
       </c>
       <c r="F4" t="n">
         <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.203745</v>
+        <v>0.203043</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2706</v>
+        <v>0.266941</v>
       </c>
       <c r="E5" t="n">
-        <v>0.227334</v>
+        <v>0.233317</v>
       </c>
       <c r="F5" t="n">
         <v>0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1206</v>
+        <v>0.116941</v>
       </c>
       <c r="H5" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.138244</v>
+        <v>0.158108</v>
       </c>
       <c r="E6" t="n">
-        <v>0.122743</v>
+        <v>0.14771</v>
       </c>
       <c r="F6" t="n">
         <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.161756</v>
+        <v>-0.141892</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.127688</v>
+        <v>0.134875</v>
       </c>
       <c r="E7" t="n">
-        <v>0.096528</v>
+        <v>0.099802</v>
       </c>
       <c r="F7" t="n">
         <v>0.35</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.222312</v>
+        <v>-0.215125</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.662899</v>
+        <v>0.656106</v>
       </c>
       <c r="E8" t="n">
-        <v>0.216022</v>
+        <v>0.219619</v>
       </c>
       <c r="F8" t="n">
         <v>0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.462899</v>
+        <v>0.456106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.071169</v>
+        <v>0.050912</v>
       </c>
       <c r="E9" t="n">
-        <v>0.098147</v>
+        <v>0.066894</v>
       </c>
       <c r="F9" t="n">
         <v>0.15</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.078831</v>
+        <v>-0.099088</v>
       </c>
       <c r="H9" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.207971</v>
+        <v>0.1937</v>
       </c>
       <c r="E10" t="n">
-        <v>0.254088</v>
+        <v>0.250845</v>
       </c>
       <c r="F10" t="n">
         <v>0.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.092029</v>
+        <v>-0.1063</v>
       </c>
       <c r="H10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -743,16 +743,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.043979</v>
+        <v>0.042827</v>
       </c>
       <c r="E11" t="n">
-        <v>0.111779</v>
+        <v>0.107885</v>
       </c>
       <c r="F11" t="n">
         <v>0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.306021</v>
+        <v>-0.307173</v>
       </c>
       <c r="H11" t="n">
         <v>42</v>
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.29187</v>
+        <v>0.297641</v>
       </c>
       <c r="E12" t="n">
-        <v>0.149941</v>
+        <v>0.15024</v>
       </c>
       <c r="F12" t="n">
         <v>0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0.09186999999999999</v>
+        <v>0.09764100000000001</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.45618</v>
+        <v>0.465832</v>
       </c>
       <c r="E13" t="n">
-        <v>0.207363</v>
+        <v>0.208877</v>
       </c>
       <c r="F13" t="n">
         <v>0.15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.30618</v>
+        <v>0.315832</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.250786</v>
+        <v>0.249504</v>
       </c>
       <c r="E14" t="n">
-        <v>0.143353</v>
+        <v>0.148257</v>
       </c>
       <c r="F14" t="n">
         <v>0.3</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.049214</v>
+        <v>-0.050496</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.245387</v>
+        <v>0.245981</v>
       </c>
       <c r="E15" t="n">
-        <v>0.133446</v>
+        <v>0.137532</v>
       </c>
       <c r="F15" t="n">
         <v>0.35</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.104613</v>
+        <v>-0.104019</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.20345</v>
+        <v>0.202649</v>
       </c>
       <c r="E16" t="n">
-        <v>0.148014</v>
+        <v>0.148197</v>
       </c>
       <c r="F16" t="n">
         <v>0.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00345</v>
+        <v>0.002649</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.300377</v>
+        <v>0.301865</v>
       </c>
       <c r="E17" t="n">
-        <v>0.147877</v>
+        <v>0.147634</v>
       </c>
       <c r="F17" t="n">
         <v>0.15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.150377</v>
+        <v>0.151865</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
